--- a/data/trans_bre/P32-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P32-Clase-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 1,66</t>
+          <t>-2,66; 1,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 2,85</t>
+          <t>-6,49; 3,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 4,0</t>
+          <t>-5,57; 3,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 1,17</t>
+          <t>-6,1; 1,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-86,9; 92,31</t>
+          <t>-90,02; 106,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-77,03; 102,21</t>
+          <t>-73,94; 102,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-83,23; 39,35</t>
+          <t>-80,27; 63,95</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 2,35</t>
+          <t>-3,0; 2,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 2,62</t>
+          <t>-7,46; 2,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 3,11</t>
+          <t>-4,61; 3,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 3,88</t>
+          <t>-3,71; 4,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-88,14; 94,18</t>
+          <t>-88,34; 78,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-72,99; 119,3</t>
+          <t>-69,86; 135,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-69,0; 208,64</t>
+          <t>-69,46; 260,92</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 5,53</t>
+          <t>-4,17; 6,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 2,09</t>
+          <t>-6,78; 1,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 10,39</t>
+          <t>-2,79; 11,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 1,32</t>
+          <t>-9,07; 1,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 317,85</t>
+          <t>-100,0; 398,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 85,97</t>
+          <t>-100,0; 70,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 418,68</t>
+          <t>-68,55; 569,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 85,54</t>
+          <t>-100,0; 103,27</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 0,82</t>
+          <t>-3,71; 0,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,82; -3,59</t>
+          <t>-8,68; -3,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,24; -0,23</t>
+          <t>-5,24; -0,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,88; -2,7</t>
+          <t>-8,83; -2,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 64,95</t>
+          <t>-100,0; 90,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-95,72; -47,28</t>
+          <t>-95,07; -47,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-82,08; 1,15</t>
+          <t>-81,7; 6,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-99,37; -52,21</t>
+          <t>-99,49; -51,48</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 6,82</t>
+          <t>-2,43; 6,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 0,53</t>
+          <t>-5,95; 0,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,06; -1,83</t>
+          <t>-7,92; -1,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,92; -0,48</t>
+          <t>-9,27; -0,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-74,1; 645,94</t>
+          <t>-76,61; 549,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-89,1; 32,25</t>
+          <t>-90,17; 35,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -26,08</t>
+          <t>-100,0; -19,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-83,16; -3,08</t>
+          <t>-83,24; 11,36</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,27; -0,83</t>
+          <t>-7,55; -0,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-19,67; -6,95</t>
+          <t>-19,24; -6,82</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-10,13; 0,43</t>
+          <t>-9,75; 0,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-23,22; 0,32</t>
+          <t>-21,1; 0,33</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-97,52; -72,1</t>
+          <t>-97,27; -65,26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-79,16; 20,13</t>
+          <t>-79,05; 26,4</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,3; -0,11</t>
+          <t>-2,47; -0,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,14; -3,08</t>
+          <t>-6,04; -2,95</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,58; -0,64</t>
+          <t>-3,52; -0,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,06; -2,39</t>
+          <t>-6,13; -2,52</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-71,98; -1,1</t>
+          <t>-73,86; -2,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-80,62; -49,29</t>
+          <t>-80,62; -47,84</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-56,82; -12,09</t>
+          <t>-59,41; -9,98</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-83,35; -43,25</t>
+          <t>-84,68; -45,18</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P32-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P32-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-2,56</t>
+          <t>-2,63</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-44,77%</t>
+          <t>-42,82%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 1,76</t>
+          <t>-2,81; 1,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 3,36</t>
+          <t>-6,29; 2,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 3,7</t>
+          <t>-5,91; 3,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 1,59</t>
+          <t>-6,39; 1,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-90,02; 106,55</t>
+          <t>-89,34; 77,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-73,94; 102,11</t>
+          <t>-77,1; 103,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-80,27; 63,95</t>
+          <t>-78,08; 55,8</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,0</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-0,06%</t>
+          <t>10,22%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 2,02</t>
+          <t>-2,97; 2,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 2,22</t>
+          <t>-6,83; 2,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 3,45</t>
+          <t>-4,63; 3,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 4,32</t>
+          <t>-3,5; 4,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-88,34; 78,9</t>
+          <t>-85,83; 117,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-69,86; 135,02</t>
+          <t>-71,96; 120,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-69,46; 260,92</t>
+          <t>-63,43; 207,81</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-4,76</t>
+          <t>-5,21</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-72,66%</t>
+          <t>-75,06%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 6,41</t>
+          <t>-4,09; 4,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 1,73</t>
+          <t>-6,44; 1,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 11,89</t>
+          <t>-3,04; 11,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 1,46</t>
+          <t>-9,52; 0,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 398,29</t>
+          <t>-100,0; 319,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 70,64</t>
+          <t>-100,0; 45,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-68,55; 569,38</t>
+          <t>-100,0; 460,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 103,27</t>
+          <t>-100,0; 45,24</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-5,14</t>
+          <t>-3,43</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-85,92%</t>
+          <t>-58,16%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 0,98</t>
+          <t>-3,68; 0,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,68; -3,48</t>
+          <t>-8,72; -3,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,24; -0,24</t>
+          <t>-5,27; -0,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,83; -2,44</t>
+          <t>-6,13; 0,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 90,65</t>
+          <t>-100,0; 79,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-95,07; -47,2</t>
+          <t>-95,3; -48,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-81,7; 6,27</t>
+          <t>-82,14; 2,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-99,49; -51,48</t>
+          <t>-87,47; 26,7</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-4,55</t>
+          <t>-5,75</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-55,98%</t>
+          <t>-63,71%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 6,51</t>
+          <t>-2,2; 6,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 0,59</t>
+          <t>-5,57; 0,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,92; -1,63</t>
+          <t>-7,9; -1,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,27; -0,23</t>
+          <t>-10,1; -1,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-76,61; 549,01</t>
+          <t>-72,36; 558,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-90,17; 35,02</t>
+          <t>-88,37; 33,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -19,85</t>
+          <t>-100,0; -7,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-83,24; 11,36</t>
+          <t>-85,54; -15,0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-7,41</t>
+          <t>-7,49</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-80,14%</t>
+          <t>-80,99%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,55; -0,91</t>
+          <t>-7,77; -1,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-19,24; -6,82</t>
+          <t>-19,76; -6,61</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 0,82</t>
+          <t>-10,5; 0,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-21,1; 0,33</t>
+          <t>-21,83; 1,38</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-97,27; -65,26</t>
+          <t>-97,29; -67,79</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-79,05; 26,4</t>
+          <t>-79,04; 18,02</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-4,11</t>
+          <t>-3,5</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-66,08%</t>
+          <t>-53,87%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,47; -0,13</t>
+          <t>-2,42; -0,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,04; -2,95</t>
+          <t>-6,08; -2,95</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,52; -0,53</t>
+          <t>-3,31; -0,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,13; -2,52</t>
+          <t>-5,28; -1,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-73,86; -2,99</t>
+          <t>-73,42; 0,01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-80,62; -47,84</t>
+          <t>-80,15; -47,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-59,41; -9,98</t>
+          <t>-57,59; -9,44</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-84,68; -45,18</t>
+          <t>-70,51; -25,75</t>
         </is>
       </c>
     </row>
